--- a/main_balance.xlsx
+++ b/main_balance.xlsx
@@ -3605,7 +3605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -3624,7 +3624,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Live steam = 914,484 lb/hr | Exhaust = 851,204 lb/hr</t>
+          <t>Live steam = 914,484 lb/hr | Exhaust = 799,951 lb/hr</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3739,11 +3739,11 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Exhaust for Evaporators</t>
+          <t>Exhaust for Pre</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>287611.1242978922</v>
+        <v>293606.3239468852</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
@@ -3754,11 +3754,11 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Exhaust for Pans</t>
+          <t>Exhaust for Evaporators</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>224066.6587253941</v>
+        <v>288279.3779740722</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
@@ -3769,11 +3769,11 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Exhaust for Heaters</t>
+          <t>Exhaust for Pans</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>264239.1057251659</v>
+        <v>55982.30142952107</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
@@ -3784,11 +3784,11 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Exhaust for Deaerator</t>
+          <t>Exhaust for Heaters</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>34753.38969792811</v>
+        <v>89236.5446421735</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
@@ -3799,11 +3799,11 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Exhaust Losses</t>
+          <t>Exhaust for Deaerator</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>40533.51392231902</v>
+        <v>34753.38969792811</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
@@ -3814,11 +3814,11 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Total Exhaust</t>
+          <t>Exhaust Losses</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>851203.7923686994</v>
+        <v>38092.89688452901</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
@@ -3826,75 +3826,75 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Total Exhaust Required</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>799950.8345751091</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>EXHAUST BALANCE</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Exhaust available from turbines</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>839489.7723985524</v>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>lb/hr</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
+          <t>Exhaust available from turbines</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>839489.7723985524</v>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>Makeup required</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>11714.01997014706</v>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="B24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>lb/hr</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>LIVE STEAM AVAILABILITY</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Live steam available from bagasse</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n">
-        <v>1071037.707301613</v>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>lb/hr</t>
-        </is>
-      </c>
+      <c r="B26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Live steam demand</t>
+          <t>Live steam available from bagasse</t>
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>914484.1237634262</v>
+        <v>1071037.707301613</v>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
@@ -3905,13 +3905,28 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
+          <t>Live steam demand</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>914484.1237634262</v>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
           <t>Surplus / (Deficit)</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B29" s="7" t="n">
         <v>156553.5835381865</v>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>lb/hr</t>
         </is>
@@ -3919,12 +3934,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3939,9 +3954,9 @@
   <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="81" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -3968,7 +3983,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>8 condensers | return = 11,682,030 lb/hr @ 134.1 °F | makeup = 1,130,437 lb/hr</t>
+          <t>8 condensers | return = 9,679,853 lb/hr @ 134.4 °F | makeup = 936,661 lb/hr</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -4048,7 +4063,7 @@
         </is>
       </c>
       <c r="C39" s="22" t="n">
-        <v>554452.8029065853</v>
+        <v>461852.4345635406</v>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
       <c r="E39" s="12" t="inlineStr"/>
@@ -4063,13 +4078,13 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>11127577.31492409</v>
+        <v>9218000.302959621</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>22344.53276089175</v>
+        <v>18510.04076899522</v>
       </c>
       <c r="E40" s="27" t="n">
-        <v>83.47616889295614</v>
+        <v>83.47581720581169</v>
       </c>
     </row>
     <row r="41">
@@ -4082,13 +4097,13 @@
         </is>
       </c>
       <c r="C41" s="22" t="n">
-        <v>11682030.11783068</v>
+        <v>9679852.737523161</v>
       </c>
       <c r="D41" s="22" t="n">
-        <v>23457.89180287284</v>
+        <v>19437.45529623124</v>
       </c>
       <c r="E41" s="24" t="n">
-        <v>134.1435088111203</v>
+        <v>134.4186035896276</v>
       </c>
     </row>
     <row r="42">
@@ -4101,10 +4116,10 @@
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>516686.355024646</v>
+        <v>430528.3247174657</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>1037.522801254309</v>
+        <v>864.5147082680032</v>
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
@@ -4118,13 +4133,13 @@
         </is>
       </c>
       <c r="C43" s="22" t="n">
-        <v>1168203.011783068</v>
+        <v>967985.2737523161</v>
       </c>
       <c r="D43" s="22" t="n">
-        <v>2345.789180287285</v>
+        <v>1943.745529623125</v>
       </c>
       <c r="E43" s="24" t="n">
-        <v>134.1435088111203</v>
+        <v>134.4186035896276</v>
       </c>
     </row>
     <row r="44">
@@ -4137,10 +4152,10 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>1130436.563901126</v>
+        <v>936661.1639062427</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>2269.952939560495</v>
+        <v>1880.845710655106</v>
       </c>
       <c r="E44" s="27" t="n">
         <v>70</v>
@@ -4227,16 +4242,16 @@
         <v>86.42507599061878</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>1443311.249831055</v>
+        <v>1443302.772987539</v>
       </c>
       <c r="G48" s="22" t="n">
-        <v>2884.315047624011</v>
+        <v>2884.298107489086</v>
       </c>
       <c r="H48" s="24" t="n">
         <v>143.355890609762</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>1528774.923816304</v>
+        <v>1528766.446972788</v>
       </c>
     </row>
     <row r="49">
@@ -4258,16 +4273,16 @@
         <v>49.42522625424751</v>
       </c>
       <c r="F49" s="25" t="n">
-        <v>825408.4160243492</v>
+        <v>825403.5682425691</v>
       </c>
       <c r="G49" s="25" t="n">
-        <v>1649.497234261289</v>
+        <v>1649.48754644798</v>
       </c>
       <c r="H49" s="27" t="n">
         <v>143.355890609762</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>874283.8306516814</v>
+        <v>874278.9828699013</v>
       </c>
     </row>
     <row r="50">
@@ -4289,16 +4304,16 @@
         <v>40.07602197251683</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>807875.1070721616</v>
+        <v>807869.3796755079</v>
       </c>
       <c r="G50" s="22" t="n">
-        <v>1614.458647226542</v>
+        <v>1614.447201589744</v>
       </c>
       <c r="H50" s="24" t="n">
         <v>133.0828737186033</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>847272.3702740214</v>
+        <v>847266.6428773677</v>
       </c>
     </row>
     <row r="51">
@@ -4320,16 +4335,16 @@
         <v>7.962371261173675</v>
       </c>
       <c r="F51" s="25" t="n">
-        <v>174677.3445253404</v>
+        <v>174675.9968543457</v>
       </c>
       <c r="G51" s="25" t="n">
-        <v>349.0754287077148</v>
+        <v>349.0727355202752</v>
       </c>
       <c r="H51" s="27" t="n">
         <v>129.059477265374</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>182486.9299094664</v>
+        <v>182485.5822384717</v>
       </c>
     </row>
     <row r="52">
@@ -4351,16 +4366,16 @@
         <v>24.87623682952647</v>
       </c>
       <c r="F52" s="22" t="n">
-        <v>687055.3252695698</v>
+        <v>687048.6518103256</v>
       </c>
       <c r="G52" s="22" t="n">
-        <v>1373.012240746542</v>
+        <v>1372.998904497053</v>
       </c>
       <c r="H52" s="24" t="n">
         <v>119.6832047961655</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>711324.9054816641</v>
+        <v>711318.2320224199</v>
       </c>
     </row>
     <row r="53">
@@ -4370,7 +4385,7 @@
         </is>
       </c>
       <c r="B53" s="25" t="n">
-        <v>194541.493415139</v>
+        <v>141020.7622348607</v>
       </c>
       <c r="C53" s="27" t="n">
         <v>132.8134936467732</v>
@@ -4379,19 +4394,19 @@
         <v>1017.385031485097</v>
       </c>
       <c r="E53" s="34" t="n">
-        <v>197.9236034033189</v>
+        <v>143.4724126263661</v>
       </c>
       <c r="F53" s="25" t="n">
-        <v>4011640.363374306</v>
+        <v>2907968.574443268</v>
       </c>
       <c r="G53" s="25" t="n">
-        <v>8016.867232962243</v>
+        <v>5811.288118391823</v>
       </c>
       <c r="H53" s="27" t="n">
         <v>132.8134936467732</v>
       </c>
       <c r="I53" s="25" t="n">
-        <v>4206181.856789446</v>
+        <v>3048989.336678129</v>
       </c>
     </row>
     <row r="54">
@@ -4401,7 +4416,7 @@
         </is>
       </c>
       <c r="B54" s="22" t="n">
-        <v>93379.91683926681</v>
+        <v>66964.39385218119</v>
       </c>
       <c r="C54" s="24" t="n">
         <v>132.8134936467732</v>
@@ -4410,19 +4425,19 @@
         <v>1017.385031485097</v>
       </c>
       <c r="E54" s="33" t="n">
-        <v>95.0033296335932</v>
+        <v>68.12857194768181</v>
       </c>
       <c r="F54" s="22" t="n">
-        <v>1925587.374419669</v>
+        <v>1380863.000899644</v>
       </c>
       <c r="G54" s="22" t="n">
-        <v>3848.096271821882</v>
+        <v>2759.518387089616</v>
       </c>
       <c r="H54" s="24" t="n">
         <v>132.8134936467732</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>2018967.291258936</v>
+        <v>1447827.394751825</v>
       </c>
     </row>
     <row r="55">
@@ -4432,7 +4447,7 @@
         </is>
       </c>
       <c r="B55" s="25" t="n">
-        <v>60715.87524151788</v>
+        <v>48051.7610658372</v>
       </c>
       <c r="C55" s="27" t="n">
         <v>132.8134936467732</v>
@@ -4441,19 +4456,19 @@
         <v>1017.385031485097</v>
       </c>
       <c r="E55" s="34" t="n">
-        <v>61.77142264423689</v>
+        <v>48.88714244488114</v>
       </c>
       <c r="F55" s="25" t="n">
-        <v>1252022.13440764</v>
+        <v>990868.3580464221</v>
       </c>
       <c r="G55" s="25" t="n">
-        <v>2502.042634707514</v>
+        <v>1980.15259401763</v>
       </c>
       <c r="H55" s="27" t="n">
         <v>132.8134936467732</v>
       </c>
       <c r="I55" s="25" t="n">
-        <v>1312738.009649158</v>
+        <v>1038920.119112259</v>
       </c>
     </row>
     <row r="56">
@@ -4463,22 +4478,22 @@
         </is>
       </c>
       <c r="B56" s="28" t="n">
-        <v>554452.8029065853</v>
+        <v>461852.4345635407</v>
       </c>
       <c r="C56" s="16" t="inlineStr"/>
       <c r="D56" s="16" t="inlineStr"/>
       <c r="E56" s="35" t="n">
-        <v>563.4632879892323</v>
+        <v>469.2530593270124</v>
       </c>
       <c r="F56" s="28" t="n">
-        <v>11127577.31492409</v>
+        <v>9218000.302959621</v>
       </c>
       <c r="G56" s="28" t="n">
-        <v>22237.36473805774</v>
+        <v>18421.26359504321</v>
       </c>
       <c r="H56" s="16" t="inlineStr"/>
       <c r="I56" s="28" t="n">
-        <v>11682030.11783068</v>
+        <v>9679852.737523161</v>
       </c>
     </row>
     <row r="57">
@@ -4488,7 +4503,7 @@
         </is>
       </c>
       <c r="B57" s="31" t="n">
-        <v>83.47616889295614</v>
+        <v>83.47581720581169</v>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
@@ -4518,7 +4533,7 @@
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>11127577.31492409</v>
+        <v>9218000.302959621</v>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
@@ -4533,7 +4548,7 @@
         </is>
       </c>
       <c r="B61" s="7" t="n">
-        <v>554452.8029065853</v>
+        <v>461852.4345635406</v>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
@@ -4548,7 +4563,7 @@
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>11682030.11783068</v>
+        <v>9679852.737523161</v>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
@@ -4563,7 +4578,7 @@
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>23457.89180287284</v>
+        <v>19437.45529623124</v>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
@@ -4578,7 +4593,7 @@
         </is>
       </c>
       <c r="B64" s="31" t="n">
-        <v>134.1435088111203</v>
+        <v>134.4186035896276</v>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
@@ -4608,7 +4623,7 @@
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>11682030.11783068</v>
+        <v>9679852.737523161</v>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
@@ -4623,7 +4638,7 @@
         </is>
       </c>
       <c r="B68" s="31" t="n">
-        <v>134.1435088111203</v>
+        <v>134.4186035896276</v>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
@@ -4653,7 +4668,7 @@
         </is>
       </c>
       <c r="B70" s="7" t="n">
-        <v>1168203.011783068</v>
+        <v>967985.2737523161</v>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
@@ -4668,7 +4683,7 @@
         </is>
       </c>
       <c r="B71" s="7" t="n">
-        <v>2345.789180287285</v>
+        <v>1943.745529623125</v>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
@@ -4683,7 +4698,7 @@
         </is>
       </c>
       <c r="B72" s="7" t="n">
-        <v>516686.355024646</v>
+        <v>430528.3247174657</v>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
@@ -4698,7 +4713,7 @@
         </is>
       </c>
       <c r="B73" s="7" t="n">
-        <v>9997140.751022965</v>
+        <v>8281339.139053378</v>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
@@ -4713,7 +4728,7 @@
         </is>
       </c>
       <c r="B74" s="7" t="n">
-        <v>20074.57982133125</v>
+        <v>16629.19505834012</v>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
@@ -4743,7 +4758,7 @@
         </is>
       </c>
       <c r="B77" s="7" t="n">
-        <v>11127577.31492409</v>
+        <v>9218000.302959621</v>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
@@ -4758,7 +4773,7 @@
         </is>
       </c>
       <c r="B78" s="7" t="n">
-        <v>9997140.751022965</v>
+        <v>8281339.139053378</v>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
@@ -4773,7 +4788,7 @@
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>1130436.563901126</v>
+        <v>936661.1639062427</v>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
@@ -4788,7 +4803,7 @@
         </is>
       </c>
       <c r="B80" s="7" t="n">
-        <v>2269.952939560495</v>
+        <v>1880.845710655106</v>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
@@ -4818,7 +4833,7 @@
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>83.47616889295614</v>
+        <v>83.47581720581169</v>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
@@ -4848,7 +4863,7 @@
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>1684889.366807712</v>
+        <v>1398513.598469783</v>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
@@ -4863,7 +4878,7 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>1684889.366807714</v>
+        <v>1398513.598469782</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
@@ -4878,7 +4893,7 @@
         </is>
       </c>
       <c r="B86" s="9" t="n">
-        <v>-2.095475792884827e-09</v>
+        <v>1.629814505577087e-09</v>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
@@ -6128,7 +6143,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -6281,7 +6296,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Juice to Heater</t>
+          <t>Juice to Exhaust Heaters</t>
         </is>
       </c>
       <c r="C39" s="22" t="n">
@@ -6315,7 +6330,7 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Hot Juice from Heater</t>
+          <t>Hot Juice from Exhaust Heaters</t>
         </is>
       </c>
       <c r="C41" s="22" t="n">
@@ -6368,7 +6383,7 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Steam to Heater</t>
+          <t>Steam to Exhaust Heaters</t>
         </is>
       </c>
       <c r="C44" s="25" t="n">
@@ -6406,7 +6421,7 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Condensate from Heater</t>
+          <t>Condensate from Exhaust Heaters</t>
         </is>
       </c>
       <c r="C46" s="25" t="n">
@@ -6507,7 +6522,7 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Exhaust</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="C50" s="22" t="n">
@@ -6544,7 +6559,7 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Heater</t>
+          <t>Exhaust Heaters</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
@@ -8581,7 +8596,7 @@
       </c>
       <c r="B123" s="30" t="inlineStr">
         <is>
-          <t>Exhaust</t>
+          <t>V1</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9409,7 @@
       </c>
       <c r="B156" s="30" t="inlineStr">
         <is>
-          <t>Exhaust</t>
+          <t>V1</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11367,7 @@
       </c>
       <c r="B236" s="30" t="inlineStr">
         <is>
-          <t>Exhaust</t>
+          <t>V1</t>
         </is>
       </c>
     </row>
@@ -12330,8 +12345,8 @@
   <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="62" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
@@ -12349,7 +12364,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>vapor bleed = 0 lb/hr | area = 35,000 ft² | U ratio = 1.000</t>
+          <t>vapor bleed = 274,470 lb/hr | area = 35,000 ft² | U ratio = 1.000</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -12412,13 +12427,13 @@
         </is>
       </c>
       <c r="B8" s="25" t="n">
-        <v>1595348.671359166</v>
+        <v>1320879.136656074</v>
       </c>
       <c r="C8" s="26" t="n">
-        <v>14.31188566616731</v>
+        <v>17.28579636738509</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>248.5074209193715</v>
+        <v>235.3160594853474</v>
       </c>
     </row>
     <row r="9">
@@ -12428,13 +12443,13 @@
         </is>
       </c>
       <c r="B9" s="22" t="n">
-        <v>0</v>
+        <v>274469.5347030924</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>28.20109059592511</v>
+        <v>22.22800262061473</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>246.7947894096885</v>
+        <v>233.6034279756644</v>
       </c>
     </row>
     <row r="10">
@@ -12444,7 +12459,7 @@
         </is>
       </c>
       <c r="B10" s="25" t="n">
-        <v>36320.23033626748</v>
+        <v>293606.3239468852</v>
       </c>
       <c r="C10" s="26" t="n">
         <v>30</v>
@@ -12470,7 +12485,7 @@
         </is>
       </c>
       <c r="B13" s="36" t="n">
-        <v>28.20109059592511</v>
+        <v>22.22800262061473</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
@@ -12485,7 +12500,7 @@
         </is>
       </c>
       <c r="B14" s="36" t="n">
-        <v>13.50509059592511</v>
+        <v>7.532002620614731</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
@@ -12500,7 +12515,7 @@
         </is>
       </c>
       <c r="B15" s="36" t="n">
-        <v>246.7947894096885</v>
+        <v>233.6034279756644</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
@@ -12530,7 +12545,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>34332395.48462067</v>
+        <v>277537018.2733821</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
@@ -12560,7 +12575,7 @@
         </is>
       </c>
       <c r="B19" s="36" t="n">
-        <v>542.7468373032524</v>
+        <v>528.6878699284482</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
@@ -12575,7 +12590,7 @@
         </is>
       </c>
       <c r="B20" s="36" t="n">
-        <v>542.7468373032565</v>
+        <v>528.6878699284479</v>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
@@ -12590,7 +12605,7 @@
         </is>
       </c>
       <c r="B21" s="29" t="n">
-        <v>1.000000000000008</v>
+        <v>0.9999999999999993</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1">
@@ -12650,7 +12665,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>3 sets  |  total steam = 287,611 lb/hr  |  total condenser injection water = 8,284,733 lb/hr (16,556 GPM)</t>
+          <t>3 sets  |  total steam = 288,279 lb/hr  |  total condenser injection water = 6,084,253 lb/hr (12,159 GPM)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -12703,13 +12718,13 @@
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>926180.5950572814</v>
+        <v>765724.6691488327</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>14.31188566616731</v>
+        <v>17.28579636738509</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>248.5074209193715</v>
+        <v>235.3160594853474</v>
       </c>
     </row>
     <row r="8">
@@ -12719,13 +12734,13 @@
         </is>
       </c>
       <c r="B8" s="25" t="n">
-        <v>203947.1260965749</v>
+        <v>203633.2990857998</v>
       </c>
       <c r="C8" s="26" t="n">
-        <v>64.99425138457603</v>
+        <v>64.99998165237724</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>148.9087072550019</v>
+        <v>148.9109379811183</v>
       </c>
     </row>
     <row r="9">
@@ -12735,7 +12750,7 @@
         </is>
       </c>
       <c r="B9" s="22" t="n">
-        <v>160485.0115180882</v>
+        <v>165639.3371727225</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>30</v>
@@ -12781,7 +12796,7 @@
         </is>
       </c>
       <c r="B12" s="29" t="n">
-        <v>1.070685713021959</v>
+        <v>0.8845258968867411</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -12827,16 +12842,16 @@
         </is>
       </c>
       <c r="B16" s="22" t="n">
-        <v>926180.5950572814</v>
+        <v>765724.6691488327</v>
       </c>
       <c r="C16" s="22" t="n">
-        <v>759132.8155193999</v>
+        <v>602529.2934535781</v>
       </c>
       <c r="D16" s="22" t="n">
-        <v>583051.520045844</v>
+        <v>477049.4182127767</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>398488.2710755402</v>
+        <v>344654.0607970578</v>
       </c>
     </row>
     <row r="17">
@@ -12846,16 +12861,16 @@
         </is>
       </c>
       <c r="B17" s="25" t="n">
-        <v>759132.8155193999</v>
+        <v>602529.2934535781</v>
       </c>
       <c r="C17" s="25" t="n">
-        <v>583051.520045844</v>
+        <v>477049.4182127767</v>
       </c>
       <c r="D17" s="25" t="n">
-        <v>398488.2710755402</v>
+        <v>344654.0607970578</v>
       </c>
       <c r="E17" s="25" t="n">
-        <v>203947.1260965749</v>
+        <v>203633.2990857998</v>
       </c>
     </row>
     <row r="18">
@@ -12865,16 +12880,16 @@
         </is>
       </c>
       <c r="B18" s="22" t="n">
-        <v>160485.0115180882</v>
+        <v>165639.3371727225</v>
       </c>
       <c r="C18" s="22" t="n">
-        <v>167047.5479530811</v>
+        <v>118594.076306002</v>
       </c>
       <c r="D18" s="22" t="n">
-        <v>176080.9086559267</v>
+        <v>125479.8752393266</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>184562.7111963997</v>
+        <v>132395.3574053553</v>
       </c>
     </row>
     <row r="19">
@@ -12884,16 +12899,16 @@
         </is>
       </c>
       <c r="B19" s="25" t="n">
-        <v>167047.782405948</v>
+        <v>163195.3756954482</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>176081.3050009334</v>
+        <v>125479.875242251</v>
       </c>
       <c r="D19" s="25" t="n">
-        <v>184563.2800685588</v>
+        <v>132395.3574307849</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>194541.493415139</v>
+        <v>141020.7622348607</v>
       </c>
     </row>
     <row r="20">
@@ -12903,7 +12918,7 @@
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>0</v>
+        <v>44601.29938925251</v>
       </c>
       <c r="C20" s="22" t="n">
         <v>0</v>
@@ -12977,16 +12992,16 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>14.31188566616731</v>
+        <v>17.28579636738509</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>17.46122748443334</v>
+        <v>21.96766339528987</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>22.73451029102947</v>
+        <v>27.74589004631457</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>33.26419306371461</v>
+        <v>38.4041919418552</v>
       </c>
     </row>
     <row r="26">
@@ -12996,16 +13011,16 @@
         </is>
       </c>
       <c r="B26" s="15" t="n">
-        <v>17.46122748443334</v>
+        <v>21.96766339528987</v>
       </c>
       <c r="C26" s="15" t="n">
-        <v>22.73451029102947</v>
+        <v>27.74589004631457</v>
       </c>
       <c r="D26" s="15" t="n">
-        <v>33.26419306371461</v>
+        <v>38.4041919418552</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>64.99425138457603</v>
+        <v>64.99998165237724</v>
       </c>
     </row>
     <row r="27">
@@ -13015,16 +13030,16 @@
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>248.5074209193715</v>
+        <v>235.3160594853474</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>239.5429588495001</v>
+        <v>236.1152313252009</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>224.2757487203992</v>
+        <v>221.1895475857327</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>202.8254354946347</v>
+        <v>199.6907200140018</v>
       </c>
     </row>
     <row r="28">
@@ -13034,16 +13049,16 @@
         </is>
       </c>
       <c r="B28" s="15" t="n">
-        <v>239.5429588495001</v>
+        <v>236.1152313252009</v>
       </c>
       <c r="C28" s="15" t="n">
-        <v>224.2757487203992</v>
+        <v>221.1895475857327</v>
       </c>
       <c r="D28" s="15" t="n">
-        <v>202.8254354946347</v>
+        <v>199.6907200140018</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>148.9087072550019</v>
+        <v>148.9109379811183</v>
       </c>
     </row>
     <row r="29">
@@ -13053,16 +13068,16 @@
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>0.9154519746721577</v>
+        <v>0.8986315357460699</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>0.8976392973480449</v>
+        <v>0.8721508958362405</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>0.8678136097939373</v>
+        <v>0.8394692458980447</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>0.8082577240316301</v>
+        <v>0.7791858903768669</v>
       </c>
     </row>
     <row r="30">
@@ -13072,16 +13087,16 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>0.8976392973480449</v>
+        <v>0.8721508958362405</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>0.8678136097939373</v>
+        <v>0.8394692458980447</v>
       </c>
       <c r="D30" s="15" t="n">
-        <v>0.8082577240316301</v>
+        <v>0.7791858903768669</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>0.628792514168838</v>
+        <v>0.6287601037741544</v>
       </c>
     </row>
     <row r="31">
@@ -13091,13 +13106,13 @@
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>23.93156289608371</v>
+        <v>22.35325542044207</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>17.82071845684144</v>
+        <v>16.61117389265828</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>11.20815507963227</v>
+        <v>10.3400478944107</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>2.400000000000002</v>
@@ -13110,13 +13125,13 @@
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>237.6403376835108</v>
+        <v>233.9140792316708</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>221.8551856408353</v>
+        <v>218.2110523627672</v>
       </c>
       <c r="D32" s="15" t="n">
-        <v>198.6042184688237</v>
+        <v>194.7449627665778</v>
       </c>
       <c r="E32" s="15" t="n">
         <v>132.8134936467732</v>
@@ -13129,13 +13144,13 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>953.6329724386698</v>
+        <v>956.0555949506886</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>963.790822171925</v>
+        <v>966.0985393878</v>
       </c>
       <c r="D33" s="13" t="n">
-        <v>978.3018273817613</v>
+        <v>980.6652285302995</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>1017.385031485097</v>
@@ -13151,13 +13166,13 @@
         <v>30</v>
       </c>
       <c r="C34" s="15" t="n">
-        <v>23.93156289608371</v>
+        <v>22.35325542044207</v>
       </c>
       <c r="D34" s="15" t="n">
-        <v>17.82071845684144</v>
+        <v>16.61117389265828</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>11.20815507963227</v>
+        <v>10.3400478944107</v>
       </c>
     </row>
     <row r="35">
@@ -13170,13 +13185,13 @@
         <v>250.3147563432844</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>237.6403376835108</v>
+        <v>233.9140792316708</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>221.8551856408353</v>
+        <v>218.2110523627672</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>198.6042184688237</v>
+        <v>194.7449627665778</v>
       </c>
     </row>
     <row r="36">
@@ -13189,13 +13204,13 @@
         <v>945.2692113116401</v>
       </c>
       <c r="C36" s="15" t="n">
-        <v>953.6329724386698</v>
+        <v>956.0555949506886</v>
       </c>
       <c r="D36" s="15" t="n">
-        <v>963.790822171925</v>
+        <v>966.0985393878</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>978.3018273817613</v>
+        <v>980.6652285302995</v>
       </c>
     </row>
     <row r="37">
@@ -13205,16 +13220,16 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>151.7015402650427</v>
+        <v>156.5737656114423</v>
       </c>
       <c r="C37" s="13" t="n">
-        <v>159.3020496930879</v>
+        <v>113.3825301803621</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>169.7051637222752</v>
+        <v>121.2259241912768</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>180.5580376299701</v>
+        <v>129.8355234262734</v>
       </c>
     </row>
     <row r="38">
@@ -13224,16 +13239,16 @@
         </is>
       </c>
       <c r="B38" s="15" t="n">
-        <v>563.3286008303817</v>
+        <v>441.0676143379183</v>
       </c>
       <c r="C38" s="15" t="n">
-        <v>476.7884747755032</v>
+        <v>356.4218576690981</v>
       </c>
       <c r="D38" s="15" t="n">
-        <v>356.7154847929696</v>
+        <v>261.8223515829249</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>145.3314661383353</v>
+        <v>113.3092928530795</v>
       </c>
     </row>
     <row r="39">
@@ -13243,16 +13258,16 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>526.1210219316741</v>
+        <v>498.6595603642349</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>445.3186586044932</v>
+        <v>402.9822058580106</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>333.1677363366769</v>
+        <v>296.0209390084281</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>135.738064395809</v>
+        <v>128.0817031642239</v>
       </c>
     </row>
     <row r="41" ht="17" customHeight="1">
@@ -13312,22 +13327,22 @@
         </is>
       </c>
       <c r="B43" s="22" t="n">
-        <v>160485.0115180882</v>
+        <v>165639.3371727225</v>
       </c>
       <c r="C43" s="24" t="n">
         <v>945.2692113116401</v>
       </c>
       <c r="D43" s="33" t="n">
-        <v>151.7015402650427</v>
+        <v>156.5737656114423</v>
       </c>
       <c r="E43" s="33" t="n">
-        <v>7.600733010029611</v>
+        <v>-0.5499136077294455</v>
       </c>
       <c r="F43" s="33" t="n">
-        <v>159.3022732750723</v>
+        <v>156.0238520037128</v>
       </c>
       <c r="G43" s="22" t="n">
-        <v>167047.782405948</v>
+        <v>163195.3756954482</v>
       </c>
     </row>
     <row r="44">
@@ -13337,22 +13352,22 @@
         </is>
       </c>
       <c r="B44" s="25" t="n">
-        <v>167047.5479530811</v>
+        <v>118594.076306002</v>
       </c>
       <c r="C44" s="27" t="n">
-        <v>953.6329724386698</v>
+        <v>956.0555949506886</v>
       </c>
       <c r="D44" s="34" t="n">
-        <v>159.3020496930879</v>
+        <v>113.3825301803621</v>
       </c>
       <c r="E44" s="34" t="n">
-        <v>10.4034960228671</v>
+        <v>7.843394013739925</v>
       </c>
       <c r="F44" s="34" t="n">
-        <v>169.7055457159551</v>
+        <v>121.225924194102</v>
       </c>
       <c r="G44" s="25" t="n">
-        <v>176081.3050009334</v>
+        <v>125479.875242251</v>
       </c>
     </row>
     <row r="45">
@@ -13362,22 +13377,22 @@
         </is>
       </c>
       <c r="B45" s="22" t="n">
-        <v>176080.9086559267</v>
+        <v>125479.8752393266</v>
       </c>
       <c r="C45" s="24" t="n">
-        <v>963.790822171925</v>
+        <v>966.0985393878</v>
       </c>
       <c r="D45" s="33" t="n">
-        <v>169.7051637222752</v>
+        <v>121.2259241912768</v>
       </c>
       <c r="E45" s="33" t="n">
-        <v>10.85343043636761</v>
+        <v>8.609599259934543</v>
       </c>
       <c r="F45" s="33" t="n">
-        <v>180.5585941586428</v>
+        <v>129.8355234512114</v>
       </c>
       <c r="G45" s="22" t="n">
-        <v>184563.2800685588</v>
+        <v>132395.3574307849</v>
       </c>
     </row>
     <row r="46">
@@ -13387,22 +13402,22 @@
         </is>
       </c>
       <c r="B46" s="25" t="n">
-        <v>184562.7111963997</v>
+        <v>132395.3574053553</v>
       </c>
       <c r="C46" s="27" t="n">
-        <v>978.3018273817613</v>
+        <v>980.6652285302995</v>
       </c>
       <c r="D46" s="34" t="n">
-        <v>180.5580376299701</v>
+        <v>129.8355234262734</v>
       </c>
       <c r="E46" s="34" t="n">
-        <v>17.36556577334886</v>
+        <v>13.63688920009272</v>
       </c>
       <c r="F46" s="34" t="n">
-        <v>197.9236034033189</v>
+        <v>143.4724126263661</v>
       </c>
       <c r="G46" s="25" t="n">
-        <v>194541.493415139</v>
+        <v>141020.7622348607</v>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
@@ -13425,7 +13440,7 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>194541.493415139</v>
+        <v>141020.7622348607</v>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
@@ -13470,7 +13485,7 @@
         </is>
       </c>
       <c r="B52" s="7" t="n">
-        <v>197923603.4033189</v>
+        <v>143472412.6263661</v>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
@@ -13515,7 +13530,7 @@
         </is>
       </c>
       <c r="B55" s="7" t="n">
-        <v>4622925.777472404</v>
+        <v>3351102.664269011</v>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
@@ -13530,7 +13545,7 @@
         </is>
       </c>
       <c r="B56" s="7" t="n">
-        <v>9238.460786315756</v>
+        <v>6696.847850257815</v>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
@@ -13545,7 +13560,7 @@
         </is>
       </c>
       <c r="B57" s="7" t="n">
-        <v>4817467.270887543</v>
+        <v>3492123.426503871</v>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
@@ -13616,13 +13631,13 @@
         </is>
       </c>
       <c r="B99" s="22" t="n">
-        <v>444566.6856274952</v>
+        <v>367416.5002697319</v>
       </c>
       <c r="C99" s="23" t="n">
-        <v>14.31188566616731</v>
+        <v>17.28579636738509</v>
       </c>
       <c r="D99" s="24" t="n">
-        <v>248.5074209193715</v>
+        <v>235.3160594853474</v>
       </c>
     </row>
     <row r="100">
@@ -13632,13 +13647,13 @@
         </is>
       </c>
       <c r="B100" s="25" t="n">
-        <v>97894.62052635562</v>
+        <v>97706.43213920855</v>
       </c>
       <c r="C100" s="26" t="n">
-        <v>64.99425138457627</v>
+        <v>65.00172677097731</v>
       </c>
       <c r="D100" s="27" t="n">
-        <v>148.908707255002</v>
+        <v>148.9116174676694</v>
       </c>
     </row>
     <row r="101">
@@ -13648,7 +13663,7 @@
         </is>
       </c>
       <c r="B101" s="22" t="n">
-        <v>77032.80552868242</v>
+        <v>81407.88195619921</v>
       </c>
       <c r="C101" s="23" t="n">
         <v>30</v>
@@ -13694,7 +13709,7 @@
         </is>
       </c>
       <c r="B104" s="29" t="n">
-        <v>1.070685713021962</v>
+        <v>0.8845462590944471</v>
       </c>
     </row>
     <row r="106" ht="17" customHeight="1">
@@ -13740,16 +13755,16 @@
         </is>
       </c>
       <c r="B108" s="22" t="n">
-        <v>444566.6856274952</v>
+        <v>367416.5002697319</v>
       </c>
       <c r="C108" s="22" t="n">
-        <v>364383.751449312</v>
+        <v>287097.8104055806</v>
       </c>
       <c r="D108" s="22" t="n">
-        <v>279864.729622005</v>
+        <v>227528.848545625</v>
       </c>
       <c r="E108" s="22" t="n">
-        <v>191274.3701162591</v>
+        <v>164670.9145401748</v>
       </c>
     </row>
     <row r="109">
@@ -13759,16 +13774,16 @@
         </is>
       </c>
       <c r="B109" s="25" t="n">
-        <v>364383.751449312</v>
+        <v>287097.8104055806</v>
       </c>
       <c r="C109" s="25" t="n">
-        <v>279864.729622005</v>
+        <v>227528.848545625</v>
       </c>
       <c r="D109" s="25" t="n">
-        <v>191274.3701162591</v>
+        <v>164670.9145401748</v>
       </c>
       <c r="E109" s="25" t="n">
-        <v>97894.62052635562</v>
+        <v>97706.43213920855</v>
       </c>
     </row>
     <row r="110">
@@ -13778,16 +13793,16 @@
         </is>
       </c>
       <c r="B110" s="22" t="n">
-        <v>77032.80552868242</v>
+        <v>81407.88195619921</v>
       </c>
       <c r="C110" s="22" t="n">
-        <v>80182.82301747901</v>
+        <v>56302.60389823044</v>
       </c>
       <c r="D110" s="22" t="n">
-        <v>84518.83615484496</v>
+        <v>59569.01741799275</v>
       </c>
       <c r="E110" s="22" t="n">
-        <v>88590.101374272</v>
+        <v>62858.01038776901</v>
       </c>
     </row>
     <row r="111">
@@ -13797,16 +13812,16 @@
         </is>
       </c>
       <c r="B111" s="25" t="n">
-        <v>80182.93555485514</v>
+        <v>80318.68818116032</v>
       </c>
       <c r="C111" s="25" t="n">
-        <v>84519.02640044813</v>
+        <v>59568.95764933827</v>
       </c>
       <c r="D111" s="25" t="n">
-        <v>88590.37443290834</v>
+        <v>62857.92201201198</v>
       </c>
       <c r="E111" s="25" t="n">
-        <v>93379.91683926681</v>
+        <v>66964.39385218119</v>
       </c>
     </row>
     <row r="112">
@@ -13816,7 +13831,7 @@
         </is>
       </c>
       <c r="B112" s="22" t="n">
-        <v>0</v>
+        <v>24016.08428652059</v>
       </c>
       <c r="C112" s="22" t="n">
         <v>0</v>
@@ -13890,16 +13905,16 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>14.31188566616731</v>
+        <v>17.28579636738509</v>
       </c>
       <c r="C117" s="13" t="n">
-        <v>17.46122748443335</v>
+        <v>22.12168318771831</v>
       </c>
       <c r="D117" s="13" t="n">
-        <v>22.73451029102948</v>
+        <v>27.91332548059868</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>33.26419306371466</v>
+        <v>38.56835813060598</v>
       </c>
     </row>
     <row r="118">
@@ -13909,16 +13924,16 @@
         </is>
       </c>
       <c r="B118" s="15" t="n">
-        <v>17.46122748443335</v>
+        <v>22.12168318771831</v>
       </c>
       <c r="C118" s="15" t="n">
-        <v>22.73451029102948</v>
+        <v>27.91332548059868</v>
       </c>
       <c r="D118" s="15" t="n">
-        <v>33.26419306371466</v>
+        <v>38.56835813060598</v>
       </c>
       <c r="E118" s="15" t="n">
-        <v>64.99425138457627</v>
+        <v>65.00172677097731</v>
       </c>
     </row>
     <row r="119">
@@ -13928,16 +13943,16 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>248.5074209193715</v>
+        <v>235.3160594853474</v>
       </c>
       <c r="C119" s="13" t="n">
-        <v>239.5429588495001</v>
+        <v>235.7514087161875</v>
       </c>
       <c r="D119" s="13" t="n">
-        <v>224.2757487203991</v>
+        <v>220.8794079351993</v>
       </c>
       <c r="E119" s="13" t="n">
-        <v>202.8254354946346</v>
+        <v>199.4350646235555</v>
       </c>
     </row>
     <row r="120">
@@ -13947,16 +13962,16 @@
         </is>
       </c>
       <c r="B120" s="15" t="n">
-        <v>239.5429588495001</v>
+        <v>235.7514087161875</v>
       </c>
       <c r="C120" s="15" t="n">
-        <v>224.2757487203991</v>
+        <v>220.8794079351993</v>
       </c>
       <c r="D120" s="15" t="n">
-        <v>202.8254354946346</v>
+        <v>199.4350646235555</v>
       </c>
       <c r="E120" s="15" t="n">
-        <v>148.908707255002</v>
+        <v>148.9116174676694</v>
       </c>
     </row>
     <row r="121">
@@ -13966,16 +13981,16 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>0.9154519746721577</v>
+        <v>0.8986315357460699</v>
       </c>
       <c r="C121" s="13" t="n">
-        <v>0.8976392973480449</v>
+        <v>0.8712797598902652</v>
       </c>
       <c r="D121" s="13" t="n">
-        <v>0.8678136097939372</v>
+        <v>0.8385222310817338</v>
       </c>
       <c r="E121" s="13" t="n">
-        <v>0.8082577240316298</v>
+        <v>0.7782573664132926</v>
       </c>
     </row>
     <row r="122">
@@ -13985,16 +14000,16 @@
         </is>
       </c>
       <c r="B122" s="15" t="n">
-        <v>0.8976392973480449</v>
+        <v>0.8712797598902652</v>
       </c>
       <c r="C122" s="15" t="n">
-        <v>0.8678136097939372</v>
+        <v>0.8385222310817338</v>
       </c>
       <c r="D122" s="15" t="n">
-        <v>0.8082577240316298</v>
+        <v>0.7782573664132926</v>
       </c>
       <c r="E122" s="15" t="n">
-        <v>0.6287925141688366</v>
+        <v>0.6287502333833523</v>
       </c>
     </row>
     <row r="123">
@@ -14004,13 +14019,13 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>23.93156289608373</v>
+        <v>22.19942707484923</v>
       </c>
       <c r="C123" s="13" t="n">
-        <v>17.82071845684142</v>
+        <v>16.50243071452586</v>
       </c>
       <c r="D123" s="13" t="n">
-        <v>11.20815507963226</v>
+        <v>10.27786604381914</v>
       </c>
       <c r="E123" s="13" t="n">
         <v>2.400000000000002</v>
@@ -14023,13 +14038,13 @@
         </is>
       </c>
       <c r="B124" s="15" t="n">
-        <v>237.6403376835108</v>
+        <v>233.5394429276998</v>
       </c>
       <c r="C124" s="15" t="n">
-        <v>221.8551856408351</v>
+        <v>217.8727886374939</v>
       </c>
       <c r="D124" s="15" t="n">
-        <v>198.6042184688236</v>
+        <v>194.4582885617382</v>
       </c>
       <c r="E124" s="15" t="n">
         <v>132.8134936467732</v>
@@ -14042,13 +14057,13 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>953.6329724386698</v>
+        <v>956.2982907332323</v>
       </c>
       <c r="C125" s="13" t="n">
-        <v>963.7908221719251</v>
+        <v>966.3120821115351</v>
       </c>
       <c r="D125" s="13" t="n">
-        <v>978.3018273817614</v>
+        <v>980.8403236992397</v>
       </c>
       <c r="E125" s="13" t="n">
         <v>1017.385031485097</v>
@@ -14064,13 +14079,13 @@
         <v>30</v>
       </c>
       <c r="C126" s="15" t="n">
-        <v>23.93156289608373</v>
+        <v>22.19942707484923</v>
       </c>
       <c r="D126" s="15" t="n">
-        <v>17.82071845684142</v>
+        <v>16.50243071452586</v>
       </c>
       <c r="E126" s="15" t="n">
-        <v>11.20815507963226</v>
+        <v>10.27786604381914</v>
       </c>
     </row>
     <row r="127">
@@ -14083,13 +14098,13 @@
         <v>250.3147563432844</v>
       </c>
       <c r="C127" s="13" t="n">
-        <v>237.6403376835108</v>
+        <v>233.5394429276998</v>
       </c>
       <c r="D127" s="13" t="n">
-        <v>221.8551856408351</v>
+        <v>217.8727886374939</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>198.6042184688236</v>
+        <v>194.4582885617382</v>
       </c>
     </row>
     <row r="128">
@@ -14102,13 +14117,13 @@
         <v>945.2692113116401</v>
       </c>
       <c r="C128" s="15" t="n">
-        <v>953.6329724386698</v>
+        <v>956.2982907332323</v>
       </c>
       <c r="D128" s="15" t="n">
-        <v>963.7908221719251</v>
+        <v>966.3120821115351</v>
       </c>
       <c r="E128" s="15" t="n">
-        <v>978.3018273817614</v>
+        <v>980.8403236992397</v>
       </c>
     </row>
     <row r="129">
@@ -14118,16 +14133,16 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>72.81673932722059</v>
+        <v>76.95236437128753</v>
       </c>
       <c r="C129" s="13" t="n">
-        <v>76.46498385268229</v>
+        <v>53.84208387170799</v>
       </c>
       <c r="D129" s="13" t="n">
-        <v>81.45847858669225</v>
+        <v>57.56226125051887</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>86.66785806238578</v>
+        <v>61.65367125582953</v>
       </c>
     </row>
     <row r="130">
@@ -14137,16 +14152,16 @@
         </is>
       </c>
       <c r="B130" s="15" t="n">
-        <v>563.3286008303824</v>
+        <v>440.3312476733724</v>
       </c>
       <c r="C130" s="15" t="n">
-        <v>476.7884747754997</v>
+        <v>354.4097883852793</v>
       </c>
       <c r="D130" s="15" t="n">
-        <v>356.7154847929708</v>
+        <v>260.1652514477176</v>
       </c>
       <c r="E130" s="15" t="n">
-        <v>145.3314661383361</v>
+        <v>112.8031053548247</v>
       </c>
     </row>
     <row r="131">
@@ -14156,16 +14171,16 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>526.121021931674</v>
+        <v>497.8016451576215</v>
       </c>
       <c r="C131" s="13" t="n">
-        <v>445.3186586044932</v>
+        <v>400.6874342581498</v>
       </c>
       <c r="D131" s="13" t="n">
-        <v>333.1677363366762</v>
+        <v>294.1523744464141</v>
       </c>
       <c r="E131" s="13" t="n">
-        <v>135.7380643958078</v>
+        <v>127.5084472941762</v>
       </c>
     </row>
     <row r="133" ht="17" customHeight="1">
@@ -14225,22 +14240,22 @@
         </is>
       </c>
       <c r="B135" s="22" t="n">
-        <v>77032.80552868242</v>
+        <v>81407.88195619921</v>
       </c>
       <c r="C135" s="24" t="n">
         <v>945.2692113116401</v>
       </c>
       <c r="D135" s="33" t="n">
-        <v>72.81673932722059</v>
+        <v>76.95236437128753</v>
       </c>
       <c r="E135" s="33" t="n">
-        <v>3.648351844814214</v>
+        <v>-0.1437401497084396</v>
       </c>
       <c r="F135" s="33" t="n">
-        <v>76.4650911720348</v>
+        <v>76.80862422157909</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>80182.93555485514</v>
+        <v>80318.68818116032</v>
       </c>
     </row>
     <row r="136">
@@ -14250,22 +14265,22 @@
         </is>
       </c>
       <c r="B136" s="25" t="n">
-        <v>80182.82301747901</v>
+        <v>56302.60389823044</v>
       </c>
       <c r="C136" s="27" t="n">
-        <v>953.6329724386698</v>
+        <v>956.2982907332323</v>
       </c>
       <c r="D136" s="34" t="n">
-        <v>76.46498385268229</v>
+        <v>53.84208387170799</v>
       </c>
       <c r="E136" s="34" t="n">
-        <v>4.993678090976247</v>
+        <v>3.720119623637931</v>
       </c>
       <c r="F136" s="34" t="n">
-        <v>81.45866194365854</v>
+        <v>57.56220349534592</v>
       </c>
       <c r="G136" s="25" t="n">
-        <v>84519.02640044813</v>
+        <v>59568.95764933827</v>
       </c>
     </row>
     <row r="137">
@@ -14275,22 +14290,22 @@
         </is>
       </c>
       <c r="B137" s="22" t="n">
-        <v>84518.83615484496</v>
+        <v>59569.01741799275</v>
       </c>
       <c r="C137" s="24" t="n">
-        <v>963.7908221719251</v>
+        <v>966.3120821115351</v>
       </c>
       <c r="D137" s="33" t="n">
-        <v>81.45847858669225</v>
+        <v>57.56226125051887</v>
       </c>
       <c r="E137" s="33" t="n">
-        <v>5.209646609456446</v>
+        <v>4.091323322804519</v>
       </c>
       <c r="F137" s="33" t="n">
-        <v>86.66812519614871</v>
+        <v>61.65358457332339</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>88590.37443290834</v>
+        <v>62857.92201201198</v>
       </c>
     </row>
     <row r="138">
@@ -14300,22 +14315,22 @@
         </is>
       </c>
       <c r="B138" s="25" t="n">
-        <v>88590.101374272</v>
+        <v>62858.01038776901</v>
       </c>
       <c r="C138" s="27" t="n">
-        <v>978.3018273817614</v>
+        <v>980.8403236992397</v>
       </c>
       <c r="D138" s="34" t="n">
-        <v>86.66785806238578</v>
+        <v>61.65367125582953</v>
       </c>
       <c r="E138" s="34" t="n">
-        <v>8.335471571207416</v>
+        <v>6.47490069185227</v>
       </c>
       <c r="F138" s="34" t="n">
-        <v>95.0033296335932</v>
+        <v>68.12857194768181</v>
       </c>
       <c r="G138" s="25" t="n">
-        <v>93379.91683926681</v>
+        <v>66964.39385218119</v>
       </c>
     </row>
     <row r="140" ht="17" customHeight="1">
@@ -14338,7 +14353,7 @@
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>93379.91683926681</v>
+        <v>66964.39385218119</v>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
@@ -14383,7 +14398,7 @@
         </is>
       </c>
       <c r="B144" s="7" t="n">
-        <v>95003329.6335932</v>
+        <v>68128571.9476818</v>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
@@ -14428,7 +14443,7 @@
         </is>
       </c>
       <c r="B147" s="7" t="n">
-        <v>2219004.373186756</v>
+        <v>1591287.375652338</v>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
@@ -14443,7 +14458,7 @@
         </is>
       </c>
       <c r="B148" s="7" t="n">
-        <v>4434.461177431568</v>
+        <v>3180.030726723297</v>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
@@ -14458,7 +14473,7 @@
         </is>
       </c>
       <c r="B149" s="7" t="n">
-        <v>2312384.290026023</v>
+        <v>1658251.769504519</v>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
@@ -14529,13 +14544,13 @@
         </is>
       </c>
       <c r="B191" s="22" t="n">
-        <v>224601.3906743896</v>
+        <v>187737.9672375094</v>
       </c>
       <c r="C191" s="23" t="n">
-        <v>14.31188566616731</v>
+        <v>17.28579636738509</v>
       </c>
       <c r="D191" s="24" t="n">
-        <v>248.5074209193715</v>
+        <v>235.3160594853474</v>
       </c>
     </row>
     <row r="192">
@@ -14545,13 +14560,13 @@
         </is>
       </c>
       <c r="B192" s="25" t="n">
-        <v>49453.44231781421</v>
+        <v>49926.11241529891</v>
       </c>
       <c r="C192" s="26" t="n">
-        <v>64.99991250631545</v>
+        <v>65.00005938976271</v>
       </c>
       <c r="D192" s="27" t="n">
-        <v>148.9109110593961</v>
+        <v>148.9109682479512</v>
       </c>
     </row>
     <row r="193">
@@ -14561,7 +14576,7 @@
         </is>
       </c>
       <c r="B193" s="22" t="n">
-        <v>50093.30725112157</v>
+        <v>41232.15884515046</v>
       </c>
       <c r="C193" s="23" t="n">
         <v>20</v>
@@ -14607,7 +14622,7 @@
         </is>
       </c>
       <c r="B196" s="29" t="n">
-        <v>1.070693793107769</v>
+        <v>0.884424111536097</v>
       </c>
     </row>
     <row r="198" ht="17" customHeight="1">
@@ -14648,13 +14663,13 @@
         </is>
       </c>
       <c r="B200" s="22" t="n">
-        <v>224601.3906743896</v>
+        <v>187737.9672375094</v>
       </c>
       <c r="C200" s="22" t="n">
-        <v>168492.8287154433</v>
+        <v>143822.3180797936</v>
       </c>
       <c r="D200" s="22" t="n">
-        <v>110169.3172199503</v>
+        <v>97977.87245313954</v>
       </c>
     </row>
     <row r="201">
@@ -14664,13 +14679,13 @@
         </is>
       </c>
       <c r="B201" s="25" t="n">
-        <v>168492.8287154433</v>
+        <v>143822.3180797936</v>
       </c>
       <c r="C201" s="25" t="n">
-        <v>110169.3172199503</v>
+        <v>97977.87245313954</v>
       </c>
       <c r="D201" s="25" t="n">
-        <v>49453.44231781421</v>
+        <v>49926.11241529891</v>
       </c>
     </row>
     <row r="202">
@@ -14680,13 +14695,13 @@
         </is>
       </c>
       <c r="B202" s="22" t="n">
-        <v>50093.30725112157</v>
+        <v>41232.15884515046</v>
       </c>
       <c r="C202" s="22" t="n">
-        <v>56108.56195894637</v>
+        <v>43915.64915771572</v>
       </c>
       <c r="D202" s="22" t="n">
-        <v>58323.511494323</v>
+        <v>45844.445620462</v>
       </c>
     </row>
     <row r="203">
@@ -14696,13 +14711,13 @@
         </is>
       </c>
       <c r="B203" s="25" t="n">
-        <v>56108.56195905429</v>
+        <v>43915.64915841683</v>
       </c>
       <c r="C203" s="25" t="n">
-        <v>58323.51149704661</v>
+        <v>45844.44563606177</v>
       </c>
       <c r="D203" s="25" t="n">
-        <v>60715.87524151788</v>
+        <v>48051.7610658372</v>
       </c>
     </row>
     <row r="204">
@@ -14775,13 +14790,13 @@
         </is>
       </c>
       <c r="B209" s="13" t="n">
-        <v>14.31188566616731</v>
+        <v>17.28579636738509</v>
       </c>
       <c r="C209" s="13" t="n">
-        <v>19.07778181600092</v>
+        <v>22.5639547145523</v>
       </c>
       <c r="D209" s="13" t="n">
-        <v>29.17753785635645</v>
+        <v>33.12176709742805</v>
       </c>
     </row>
     <row r="210">
@@ -14791,13 +14806,13 @@
         </is>
       </c>
       <c r="B210" s="15" t="n">
-        <v>19.07778181600092</v>
+        <v>22.5639547145523</v>
       </c>
       <c r="C210" s="15" t="n">
-        <v>29.17753785635645</v>
+        <v>33.12176709742805</v>
       </c>
       <c r="D210" s="15" t="n">
-        <v>64.99991250631545</v>
+        <v>65.00005938976271</v>
       </c>
     </row>
     <row r="211">
@@ -14807,13 +14822,13 @@
         </is>
       </c>
       <c r="B211" s="13" t="n">
-        <v>248.5074209193715</v>
+        <v>235.3160594853474</v>
       </c>
       <c r="C211" s="13" t="n">
-        <v>218.3502502288849</v>
+        <v>217.9581222398996</v>
       </c>
       <c r="D211" s="13" t="n">
-        <v>198.9815241575451</v>
+        <v>198.1208972186392</v>
       </c>
     </row>
     <row r="212">
@@ -14823,13 +14838,13 @@
         </is>
       </c>
       <c r="B212" s="15" t="n">
-        <v>218.3502502288849</v>
+        <v>217.9581222398996</v>
       </c>
       <c r="C212" s="15" t="n">
-        <v>198.9815241575451</v>
+        <v>198.1208972186392</v>
       </c>
       <c r="D212" s="15" t="n">
-        <v>148.9109110593961</v>
+        <v>148.9109682479512</v>
       </c>
     </row>
     <row r="213">
@@ -14839,13 +14854,13 @@
         </is>
       </c>
       <c r="B213" s="13" t="n">
-        <v>0.9154519746721577</v>
+        <v>0.8986315357460699</v>
       </c>
       <c r="C213" s="13" t="n">
-        <v>0.8884960660486987</v>
+        <v>0.8687782721344922</v>
       </c>
       <c r="D213" s="13" t="n">
-        <v>0.8313718458844479</v>
+        <v>0.8090632852969469</v>
       </c>
     </row>
     <row r="214">
@@ -14855,13 +14870,13 @@
         </is>
       </c>
       <c r="B214" s="15" t="n">
-        <v>0.8884960660486987</v>
+        <v>0.8687782721344922</v>
       </c>
       <c r="C214" s="15" t="n">
-        <v>0.8313718458844479</v>
+        <v>0.8090632852969469</v>
       </c>
       <c r="D214" s="15" t="n">
-        <v>0.6287604948642798</v>
+        <v>0.6287596640915021</v>
       </c>
     </row>
     <row r="215">
@@ -14871,10 +14886,10 @@
         </is>
       </c>
       <c r="B215" s="13" t="n">
-        <v>15.90068161859305</v>
+        <v>15.69209422651473</v>
       </c>
       <c r="C215" s="13" t="n">
-        <v>10.40408981597911</v>
+        <v>10.12285367888355</v>
       </c>
       <c r="D215" s="13" t="n">
         <v>2.399999999999999</v>
@@ -14887,10 +14902,10 @@
         </is>
       </c>
       <c r="B216" s="15" t="n">
-        <v>215.9669011235237</v>
+        <v>215.2923138312913</v>
       </c>
       <c r="C216" s="15" t="n">
-        <v>195.0387137819358</v>
+        <v>193.7372941394968</v>
       </c>
       <c r="D216" s="15" t="n">
         <v>132.8134936467732</v>
@@ -14903,10 +14918,10 @@
         </is>
       </c>
       <c r="B217" s="13" t="n">
-        <v>967.5131644682361</v>
+        <v>967.9374450675198</v>
       </c>
       <c r="C217" s="13" t="n">
-        <v>980.4857454007799</v>
+        <v>981.2804154219028</v>
       </c>
       <c r="D217" s="13" t="n">
         <v>1017.385031485097</v>
@@ -14922,10 +14937,10 @@
         <v>20</v>
       </c>
       <c r="C218" s="15" t="n">
-        <v>15.90068161859305</v>
+        <v>15.69209422651473</v>
       </c>
       <c r="D218" s="15" t="n">
-        <v>10.40408981597911</v>
+        <v>10.12285367888355</v>
       </c>
     </row>
     <row r="219">
@@ -14938,10 +14953,10 @@
         <v>227.9344805631815</v>
       </c>
       <c r="C219" s="13" t="n">
-        <v>215.9669011235237</v>
+        <v>215.2923138312913</v>
       </c>
       <c r="D219" s="13" t="n">
-        <v>195.0387137819358</v>
+        <v>193.7372941394968</v>
       </c>
     </row>
     <row r="220">
@@ -14954,10 +14969,10 @@
         <v>959.9107191910837</v>
       </c>
       <c r="C220" s="15" t="n">
-        <v>967.5131644682361</v>
+        <v>967.9374450675198</v>
       </c>
       <c r="D220" s="15" t="n">
-        <v>980.4857454007799</v>
+        <v>981.2804154219028</v>
       </c>
     </row>
     <row r="221">
@@ -14967,13 +14982,13 @@
         </is>
       </c>
       <c r="B221" s="13" t="n">
-        <v>48.08510259008403</v>
+        <v>39.57919125084938</v>
       </c>
       <c r="C221" s="13" t="n">
-        <v>54.2857723346623</v>
+        <v>42.50760124420093</v>
       </c>
       <c r="D221" s="13" t="n">
-        <v>57.18537164190224</v>
+        <v>44.98625664323378</v>
       </c>
     </row>
     <row r="222">
@@ -14983,13 +14998,13 @@
         </is>
       </c>
       <c r="B222" s="15" t="n">
-        <v>456.1005746170578</v>
+        <v>360.6634985368204</v>
       </c>
       <c r="C222" s="15" t="n">
-        <v>355.1144312964409</v>
+        <v>275.0539988314773</v>
       </c>
       <c r="D222" s="15" t="n">
-        <v>137.7462139407049</v>
+        <v>111.5075318118373</v>
       </c>
     </row>
     <row r="223">
@@ -14999,13 +15014,13 @@
         </is>
       </c>
       <c r="B223" s="13" t="n">
-        <v>425.978599035937</v>
+        <v>407.8059662620829</v>
       </c>
       <c r="C223" s="13" t="n">
-        <v>331.6431808143862</v>
+        <v>310.9677216122611</v>
       </c>
       <c r="D223" s="13" t="n">
-        <v>128.6630691831658</v>
+        <v>126.0879987351427</v>
       </c>
     </row>
     <row r="225" ht="17" customHeight="1">
@@ -15065,22 +15080,22 @@
         </is>
       </c>
       <c r="B227" s="22" t="n">
-        <v>50093.30725112157</v>
+        <v>41232.15884515046</v>
       </c>
       <c r="C227" s="24" t="n">
         <v>959.9107191910837</v>
       </c>
       <c r="D227" s="33" t="n">
-        <v>48.08510259008403</v>
+        <v>39.57919125084938</v>
       </c>
       <c r="E227" s="33" t="n">
-        <v>6.200669744682684</v>
+        <v>2.928409994030188</v>
       </c>
       <c r="F227" s="33" t="n">
-        <v>54.28577233476672</v>
+        <v>42.50760124487957</v>
       </c>
       <c r="G227" s="22" t="n">
-        <v>56108.56195905429</v>
+        <v>43915.64915841683</v>
       </c>
     </row>
     <row r="228">
@@ -15090,22 +15105,22 @@
         </is>
       </c>
       <c r="B228" s="25" t="n">
-        <v>56108.56195894637</v>
+        <v>43915.64915771572</v>
       </c>
       <c r="C228" s="27" t="n">
-        <v>967.5131644682361</v>
+        <v>967.9374450675198</v>
       </c>
       <c r="D228" s="34" t="n">
-        <v>54.2857723346623</v>
+        <v>42.50760124420093</v>
       </c>
       <c r="E228" s="34" t="n">
-        <v>2.899599309910412</v>
+        <v>2.478655414340603</v>
       </c>
       <c r="F228" s="34" t="n">
-        <v>57.1853716445727</v>
+        <v>44.98625665854153</v>
       </c>
       <c r="G228" s="25" t="n">
-        <v>58323.51149704661</v>
+        <v>45844.44563606177</v>
       </c>
     </row>
     <row r="229">
@@ -15115,22 +15130,22 @@
         </is>
       </c>
       <c r="B229" s="22" t="n">
-        <v>58323.511494323</v>
+        <v>45844.445620462</v>
       </c>
       <c r="C229" s="24" t="n">
-        <v>980.4857454007799</v>
+        <v>981.2804154219028</v>
       </c>
       <c r="D229" s="33" t="n">
-        <v>57.18537164190224</v>
+        <v>44.98625664323378</v>
       </c>
       <c r="E229" s="33" t="n">
-        <v>4.586051002334649</v>
+        <v>3.900885801647356</v>
       </c>
       <c r="F229" s="33" t="n">
-        <v>61.77142264423689</v>
+        <v>48.88714244488114</v>
       </c>
       <c r="G229" s="22" t="n">
-        <v>60715.87524151788</v>
+        <v>48051.7610658372</v>
       </c>
     </row>
     <row r="231" ht="17" customHeight="1">
@@ -15153,7 +15168,7 @@
         </is>
       </c>
       <c r="B232" s="7" t="n">
-        <v>60715.87524151788</v>
+        <v>48051.7610658372</v>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
@@ -15198,7 +15213,7 @@
         </is>
       </c>
       <c r="B235" s="7" t="n">
-        <v>61771422.64423689</v>
+        <v>48887142.44488114</v>
       </c>
       <c r="C235" s="8" t="inlineStr">
         <is>
@@ -15243,7 +15258,7 @@
         </is>
       </c>
       <c r="B238" s="7" t="n">
-        <v>1442802.662961203</v>
+        <v>1141862.956763533</v>
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
@@ -15258,7 +15273,7 @@
         </is>
       </c>
       <c r="B239" s="7" t="n">
-        <v>2883.298686972829</v>
+        <v>2281.900393212496</v>
       </c>
       <c r="C239" s="8" t="inlineStr">
         <is>
@@ -15273,7 +15288,7 @@
         </is>
       </c>
       <c r="B240" s="7" t="n">
-        <v>1503518.538202721</v>
+        <v>1189914.71782937</v>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>

--- a/main_balance.xlsx
+++ b/main_balance.xlsx
@@ -3625,7 +3625,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>8 condensers | return = 9,679,853 lb/hr @ 134.4 °F | makeup = 936,661 lb/hr</t>
+          <t>8 condensers | return = 10,755,536 lb/hr @ 129.3 °F | makeup = 1,042,797 lb/hr</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3720,13 +3720,13 @@
         </is>
       </c>
       <c r="C40" s="25" t="n">
-        <v>9218000.302959621</v>
+        <v>10293683.5372025</v>
       </c>
       <c r="D40" s="25" t="n">
-        <v>18510.04076899522</v>
+        <v>20670.04726345883</v>
       </c>
       <c r="E40" s="27" t="n">
-        <v>83.47581720581169</v>
+        <v>83.48043221691825</v>
       </c>
     </row>
     <row r="41">
@@ -3739,13 +3739,13 @@
         </is>
       </c>
       <c r="C41" s="22" t="n">
-        <v>9679852.737523161</v>
+        <v>10755535.97176604</v>
       </c>
       <c r="D41" s="22" t="n">
-        <v>19437.45529623124</v>
+        <v>21597.46179069485</v>
       </c>
       <c r="E41" s="24" t="n">
-        <v>134.4186035896276</v>
+        <v>129.3281277734005</v>
       </c>
     </row>
     <row r="42">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="C42" s="25" t="n">
-        <v>430528.3247174657</v>
+        <v>429095.4955450651</v>
       </c>
       <c r="D42" s="25" t="n">
-        <v>864.5147082680032</v>
+        <v>861.6375412551508</v>
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
@@ -3775,13 +3775,13 @@
         </is>
       </c>
       <c r="C43" s="22" t="n">
-        <v>967985.2737523161</v>
+        <v>1075553.597176604</v>
       </c>
       <c r="D43" s="22" t="n">
-        <v>1943.745529623125</v>
+        <v>2159.746179069485</v>
       </c>
       <c r="E43" s="24" t="n">
-        <v>134.4186035896276</v>
+        <v>129.3281277734005</v>
       </c>
     </row>
     <row r="44">
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="C44" s="25" t="n">
-        <v>936661.1639062427</v>
+        <v>1042796.658158127</v>
       </c>
       <c r="D44" s="25" t="n">
-        <v>1880.845710655106</v>
+        <v>2093.969193088609</v>
       </c>
       <c r="E44" s="27" t="n">
         <v>70</v>
@@ -3881,19 +3881,19 @@
         <v>1011.249247318053</v>
       </c>
       <c r="E48" s="33" t="n">
-        <v>86.42507599061878</v>
+        <v>86.85239436054502</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>1443302.772987539</v>
+        <v>1582718.339021135</v>
       </c>
       <c r="G48" s="22" t="n">
-        <v>2884.298107489086</v>
+        <v>3162.906352959903</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>143.355890609762</v>
+        <v>138.355890609762</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>1528766.446972788</v>
+        <v>1668182.013006385</v>
       </c>
     </row>
     <row r="49">
@@ -3912,19 +3912,19 @@
         <v>1011.249247318053</v>
       </c>
       <c r="E49" s="34" t="n">
-        <v>49.42522625424751</v>
+        <v>49.66960332738417</v>
       </c>
       <c r="F49" s="25" t="n">
-        <v>825403.5682425691</v>
+        <v>905133.2741825728</v>
       </c>
       <c r="G49" s="25" t="n">
-        <v>1649.48754644798</v>
+        <v>1808.819492770929</v>
       </c>
       <c r="H49" s="27" t="n">
-        <v>143.355890609762</v>
+        <v>138.355890609762</v>
       </c>
       <c r="I49" s="25" t="n">
-        <v>874278.9828699013</v>
+        <v>954008.6888099051</v>
       </c>
     </row>
     <row r="50">
@@ -3943,19 +3943,19 @@
         <v>1017.228576695272</v>
       </c>
       <c r="E50" s="33" t="n">
-        <v>40.07602197251683</v>
+        <v>40.27300828852613</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>807869.3796755079</v>
+        <v>902932.8201014427</v>
       </c>
       <c r="G50" s="22" t="n">
-        <v>1614.447201589744</v>
+        <v>1804.422102520869</v>
       </c>
       <c r="H50" s="24" t="n">
-        <v>133.0828737186033</v>
+        <v>128.0828737186033</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>847266.6428773677</v>
+        <v>942330.0833033025</v>
       </c>
     </row>
     <row r="51">
@@ -3974,19 +3974,19 @@
         <v>1019.563890979194</v>
       </c>
       <c r="E51" s="34" t="n">
-        <v>7.962371261173675</v>
+        <v>8.001419188094305</v>
       </c>
       <c r="F51" s="25" t="n">
-        <v>174675.9968543457</v>
+        <v>197181.06176574</v>
       </c>
       <c r="G51" s="25" t="n">
-        <v>349.0727355202752</v>
+        <v>394.0468860226619</v>
       </c>
       <c r="H51" s="27" t="n">
-        <v>129.059477265374</v>
+        <v>124.059477265374</v>
       </c>
       <c r="I51" s="25" t="n">
-        <v>182485.5822384717</v>
+        <v>204990.6471498659</v>
       </c>
     </row>
     <row r="52">
@@ -4005,19 +4005,19 @@
         <v>1024.996584701115</v>
       </c>
       <c r="E52" s="33" t="n">
-        <v>24.87623682952647</v>
+        <v>24.99758473058694</v>
       </c>
       <c r="F52" s="22" t="n">
-        <v>687048.6518103256</v>
+        <v>801133.4463019063</v>
       </c>
       <c r="G52" s="22" t="n">
-        <v>1372.998904497053</v>
+        <v>1600.986103720836</v>
       </c>
       <c r="H52" s="24" t="n">
-        <v>119.6832047961655</v>
+        <v>114.6832047961655</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>711318.2320224199</v>
+        <v>825403.0265140006</v>
       </c>
     </row>
     <row r="53">
@@ -4036,19 +4036,19 @@
         <v>1017.385031485097</v>
       </c>
       <c r="E53" s="34" t="n">
-        <v>143.4724126263661</v>
+        <v>144.1775164375404</v>
       </c>
       <c r="F53" s="25" t="n">
-        <v>2907968.574443268</v>
+        <v>3252144.376847562</v>
       </c>
       <c r="G53" s="25" t="n">
-        <v>5811.288118391823</v>
+        <v>6499.089482109436</v>
       </c>
       <c r="H53" s="27" t="n">
-        <v>132.8134936467732</v>
+        <v>127.8134936467732</v>
       </c>
       <c r="I53" s="25" t="n">
-        <v>3048989.336678129</v>
+        <v>3393165.139082422</v>
       </c>
     </row>
     <row r="54">
@@ -4067,19 +4067,19 @@
         <v>1017.385031485097</v>
       </c>
       <c r="E54" s="33" t="n">
-        <v>68.12857194768181</v>
+        <v>68.46339391694271</v>
       </c>
       <c r="F54" s="22" t="n">
-        <v>1380863.000899644</v>
+        <v>1544296.552252937</v>
       </c>
       <c r="G54" s="22" t="n">
-        <v>2759.518387089616</v>
+        <v>3086.12420514176</v>
       </c>
       <c r="H54" s="24" t="n">
-        <v>132.8134936467732</v>
+        <v>127.8134936467732</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>1447827.394751825</v>
+        <v>1611260.946105118</v>
       </c>
     </row>
     <row r="55">
@@ -4098,19 +4098,19 @@
         <v>1017.385031485097</v>
       </c>
       <c r="E55" s="34" t="n">
-        <v>48.88714244488114</v>
+        <v>49.12740125021033</v>
       </c>
       <c r="F55" s="25" t="n">
-        <v>990868.3580464221</v>
+        <v>1108143.666729201</v>
       </c>
       <c r="G55" s="25" t="n">
-        <v>1980.15259401763</v>
+        <v>2214.515720881696</v>
       </c>
       <c r="H55" s="27" t="n">
-        <v>132.8134936467732</v>
+        <v>127.8134936467732</v>
       </c>
       <c r="I55" s="25" t="n">
-        <v>1038920.119112259</v>
+        <v>1156195.427795038</v>
       </c>
     </row>
     <row r="56">
@@ -4125,17 +4125,17 @@
       <c r="C56" s="16" t="inlineStr"/>
       <c r="D56" s="16" t="inlineStr"/>
       <c r="E56" s="35" t="n">
-        <v>469.2530593270124</v>
+        <v>471.56232149983</v>
       </c>
       <c r="F56" s="28" t="n">
-        <v>9218000.302959621</v>
+        <v>10293683.5372025</v>
       </c>
       <c r="G56" s="28" t="n">
-        <v>18421.26359504321</v>
+        <v>20570.91034612809</v>
       </c>
       <c r="H56" s="16" t="inlineStr"/>
       <c r="I56" s="28" t="n">
-        <v>9679852.737523161</v>
+        <v>10755535.97176604</v>
       </c>
     </row>
     <row r="57">
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="B57" s="30" t="n">
-        <v>83.47581720581169</v>
+        <v>83.48043221691825</v>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>9218000.302959621</v>
+        <v>10293683.5372025</v>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="B62" s="7" t="n">
-        <v>9679852.737523161</v>
+        <v>10755535.97176604</v>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>19437.45529623124</v>
+        <v>21597.46179069485</v>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="B64" s="30" t="n">
-        <v>134.4186035896276</v>
+        <v>129.3281277734005</v>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>9679852.737523161</v>
+        <v>10755535.97176604</v>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="B68" s="30" t="n">
-        <v>134.4186035896276</v>
+        <v>129.3281277734005</v>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="B70" s="7" t="n">
-        <v>967985.2737523161</v>
+        <v>1075553.597176604</v>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="B71" s="7" t="n">
-        <v>1943.745529623125</v>
+        <v>2159.746179069485</v>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="B72" s="7" t="n">
-        <v>430528.3247174657</v>
+        <v>429095.4955450651</v>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="B73" s="7" t="n">
-        <v>8281339.139053378</v>
+        <v>9250886.879044369</v>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="B74" s="7" t="n">
-        <v>16629.19505834012</v>
+        <v>18576.07807037021</v>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="B77" s="7" t="n">
-        <v>9218000.302959621</v>
+        <v>10293683.5372025</v>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="B78" s="7" t="n">
-        <v>8281339.139053378</v>
+        <v>9250886.879044369</v>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="B79" s="7" t="n">
-        <v>936661.1639062427</v>
+        <v>1042796.658158127</v>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="B80" s="7" t="n">
-        <v>1880.845710655106</v>
+        <v>2093.969193088609</v>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="B82" s="30" t="n">
-        <v>83.47581720581169</v>
+        <v>83.48043221691825</v>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>1398513.598469783</v>
+        <v>1504649.092721668</v>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>1398513.598469782</v>
+        <v>1504649.092721669</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="B86" s="9" t="n">
-        <v>1.629814505577087e-09</v>
+        <v>-1.164153218269348e-09</v>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.14" customWidth="1" min="1" max="1"/>
@@ -6544,221 +6544,220 @@
           <t>Juice (lb/hr)</t>
         </is>
       </c>
-      <c r="B50" s="22" t="n">
+      <c r="B50" s="13" t="n">
         <v>1444925.45971979</v>
       </c>
-      <c r="C50" s="22" t="n">
+      <c r="C50" s="13" t="n">
         <v>481641.8199065967</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Duty (BTU/hr)</t>
-        </is>
-      </c>
-      <c r="B51" s="25" t="n">
-        <v>165414648.662544</v>
-      </c>
-      <c r="C51" s="25" t="n">
-        <v>55138216.220848</v>
+          <t>Juice cp (BTU/lb·°F)</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="n">
+        <v>0.9158376858810273</v>
+      </c>
+      <c r="C51" s="15" t="n">
+        <v>0.9158376858810273</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Req Area (ft²)</t>
-        </is>
-      </c>
-      <c r="B52" s="22" t="n">
-        <v>10812.69185736374</v>
-      </c>
-      <c r="C52" s="22" t="n">
-        <v>3604.230619121246</v>
+          <t>Juice ΔT (°F)</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="C52" s="13" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Inst Area (ft²)</t>
-        </is>
-      </c>
-      <c r="B53" s="25" t="n">
-        <v>11000</v>
-      </c>
-      <c r="C53" s="25" t="n">
-        <v>5000</v>
+          <t>Duty (BTU/hr)</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="n">
+        <v>165414648.662544</v>
+      </c>
+      <c r="C53" s="15" t="n">
+        <v>55138216.220848</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
+          <t>Req Area (ft²)</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="n">
+        <v>10812.69185736374</v>
+      </c>
+      <c r="C54" s="13" t="n">
+        <v>3604.230619121246</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Inst Area (ft²)</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
           <t>Steam (lb/hr)</t>
         </is>
       </c>
-      <c r="B54" s="22" t="n">
+      <c r="B56" s="13" t="n">
         <v>175002.5610829924</v>
       </c>
-      <c r="C54" s="22" t="n">
+      <c r="C56" s="13" t="n">
         <v>58334.1870276641</v>
       </c>
     </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>HEATER CONDITIONS</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="5" t="n"/>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="5" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr"/>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr"/>
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>V1 Heaters</t>
         </is>
       </c>
-      <c r="C57" s="11" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>Exhaust Heaters</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>Steam Type</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="C58" s="12" t="inlineStr">
-        <is>
-          <t>Exhaust</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>T in (°F)</t>
-        </is>
-      </c>
-      <c r="B59" s="15" t="n">
-        <v>95</v>
-      </c>
-      <c r="C59" s="15" t="n">
-        <v>95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>T out (°F)</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="n">
-        <v>220</v>
-      </c>
-      <c r="C60" s="13" t="n">
-        <v>220</v>
+          <t>Steam Type</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>LMTD (°F)</t>
+          <t>T in (°F)</t>
         </is>
       </c>
       <c r="B61" s="15" t="n">
-        <v>76.49096582267444</v>
+        <v>95</v>
       </c>
       <c r="C61" s="15" t="n">
-        <v>76.49096582267444</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>U (BTU/hr·ft²·°F)</t>
+          <t>T out (°F)</t>
         </is>
       </c>
       <c r="B62" s="13" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C62" s="13" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
         <is>
+          <t>LMTD (°F)</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="n">
+        <v>76.49096582267444</v>
+      </c>
+      <c r="C63" s="15" t="n">
+        <v>76.49096582267444</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>U (BTU/hr·ft²·°F)</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="n">
+        <v>200</v>
+      </c>
+      <c r="C64" s="13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
           <t>Steam (psia)</t>
         </is>
       </c>
-      <c r="B63" s="15" t="n">
+      <c r="B65" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="C63" s="15" t="n">
+      <c r="C65" s="15" t="n">
         <v>30</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Total duty</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="n">
-        <v>220552864.883392</v>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>BTU/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Total steam</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="n">
-        <v>233336.7481106565</v>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>lb/hr</t>
-        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Juice split between heaters</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>75% / 25%</t>
+          <t>Total duty</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>220552864.883392</v>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>BTU/hr</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Hot juice out</t>
+          <t>Total steam</t>
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>1926567.279626387</v>
+        <v>233336.7481106565</v>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
@@ -6769,69 +6768,96 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
+          <t>Juice split between heaters</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>75% / 25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Hot juice out</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>1926567.279626387</v>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
           <t>Hot juice temperature</t>
         </is>
       </c>
-      <c r="B68" s="30" t="n">
+      <c r="B70" s="30" t="n">
         <v>220</v>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>°F</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="4" t="inlineStr">
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>CONDENSATE RETURN</t>
         </is>
       </c>
-      <c r="B70" s="5" t="n"/>
-      <c r="C70" s="5" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Clean condensate (Exhaust steam heaters)</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="n">
-        <v>56030.81829974123</v>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>lb/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Dirty condensate (V1-V4 steam heaters)</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="n">
-        <v>168092.4548992238</v>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>lb/hr</t>
-        </is>
-      </c>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
+          <t>Clean condensate (Exhaust steam heaters)</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>56030.81829974123</v>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Dirty condensate (V1-V4 steam heaters)</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>168092.4548992238</v>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
           <t>Total condensate</t>
         </is>
       </c>
-      <c r="B73" s="7" t="n">
+      <c r="B75" s="7" t="n">
         <v>224123.273198965</v>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>lb/hr</t>
         </is>
@@ -6842,10 +6868,10 @@
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A72:E72"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A70:E70"/>
-    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A58:E58"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -6862,7 +6888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34.14" customWidth="1" min="1" max="1"/>
@@ -7041,242 +7067,262 @@
           <t>Juice (lb/hr)</t>
         </is>
       </c>
-      <c r="B44" s="22" t="n">
+      <c r="B44" s="13" t="n">
         <v>1595348.671359166</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Duty (BTU/hr)</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="n">
-        <v>29209301.82972704</v>
+          <t>Juice cp (BTU/lb·°F)</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="n">
+        <v>0.9154519746721577</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Req Area (ft²)</t>
-        </is>
-      </c>
-      <c r="B46" s="22" t="n">
-        <v>4598.350953494461</v>
+          <t>Juice ΔT (°F)</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Inst Area (ft²)</t>
-        </is>
-      </c>
-      <c r="B47" s="25" t="n">
-        <v>6000</v>
+          <t>Duty (BTU/hr)</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n">
+        <v>29209301.82972704</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
+          <t>Req Area (ft²)</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>4598.350953494461</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Inst Area (ft²)</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
           <t>Steam (lb/hr)</t>
         </is>
       </c>
-      <c r="B48" s="22" t="n">
+      <c r="B50" s="13" t="n">
         <v>30902.3576145094</v>
       </c>
     </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>HEATER CONDITIONS</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="n"/>
-      <c r="E50" s="5" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr"/>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr"/>
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>Clarified Juice Heater</t>
         </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>Steam Type</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t>Exhaust</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>T in (°F)</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="n">
-        <v>205</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>T out (°F)</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="n">
-        <v>225</v>
+          <t>Steam Type</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Exhaust</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>LMTD (°F)</t>
+          <t>T in (°F)</t>
         </is>
       </c>
       <c r="B55" s="15" t="n">
-        <v>34.33581290234913</v>
+        <v>205</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>U (BTU/hr·ft²·°F)</t>
+          <t>T out (°F)</t>
         </is>
       </c>
       <c r="B56" s="13" t="n">
-        <v>185</v>
+        <v>225</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
+          <t>LMTD (°F)</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="n">
+        <v>34.33581290234913</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>U (BTU/hr·ft²·°F)</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
           <t>Steam (psia)</t>
         </is>
       </c>
-      <c r="B57" s="15" t="n">
+      <c r="B59" s="15" t="n">
         <v>30</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>Total duty</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="n">
-        <v>29209301.82972704</v>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>BTU/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Total steam</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="n">
-        <v>30902.3576145094</v>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
-        <is>
-          <t>lb/hr</t>
-        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Hot juice out</t>
+          <t>Total duty</t>
         </is>
       </c>
       <c r="B60" s="7" t="n">
-        <v>1595348.671359166</v>
+        <v>29209301.82972704</v>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>lb/hr</t>
+          <t>BTU/hr</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
+          <t>Total steam</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>30902.3576145094</v>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Hot juice out</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>1595348.671359166</v>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
           <t>Hot juice temperature</t>
         </is>
       </c>
-      <c r="B61" s="30" t="n">
+      <c r="B63" s="30" t="n">
         <v>225</v>
       </c>
-      <c r="C61" s="8" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>°F</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>CONDENSATE RETURN</t>
         </is>
       </c>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="5" t="n"/>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Clean condensate (Exhaust steam heaters)</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="n">
-        <v>29682.1550579092</v>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>lb/hr</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Dirty condensate (V1-V4 steam heaters)</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>lb/hr</t>
-        </is>
-      </c>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Total condensate</t>
+          <t>Clean condensate (Exhaust steam heaters)</t>
         </is>
       </c>
       <c r="B66" s="7" t="n">
         <v>29682.1550579092</v>
       </c>
       <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Dirty condensate (V1-V4 steam heaters)</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>lb/hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Total condensate</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>29682.1550579092</v>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>lb/hr</t>
         </is>
@@ -7285,10 +7331,10 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A65:E65"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A63:E63"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
   </mergeCells>
@@ -12364,19 +12410,19 @@
         <v>1011.249247318053</v>
       </c>
       <c r="E267" s="33" t="n">
-        <v>86.42507599061878</v>
+        <v>86.85239436054502</v>
       </c>
       <c r="F267" s="22" t="n">
-        <v>1619785.088449194</v>
+        <v>1796107.842609179</v>
       </c>
       <c r="G267" s="22" t="n">
-        <v>3236.980592424448</v>
+        <v>3589.344209850479</v>
       </c>
       <c r="H267" s="24" t="n">
-        <v>143.355890609762</v>
+        <v>138.355890609762</v>
       </c>
       <c r="I267" s="22" t="n">
-        <v>1705248.762434443</v>
+        <v>1881571.516594429</v>
       </c>
     </row>
     <row r="268">
@@ -12395,19 +12441,19 @@
         <v>1011.249247318053</v>
       </c>
       <c r="E268" s="34" t="n">
-        <v>49.42522625424751</v>
+        <v>49.66960332738417</v>
       </c>
       <c r="F268" s="25" t="n">
-        <v>926331.2014738389</v>
+        <v>1027167.583950093</v>
       </c>
       <c r="G268" s="25" t="n">
-        <v>1851.181457781453</v>
+        <v>2052.693013489394</v>
       </c>
       <c r="H268" s="27" t="n">
-        <v>143.355890609762</v>
+        <v>138.355890609762</v>
       </c>
       <c r="I268" s="25" t="n">
-        <v>975206.6161011711</v>
+        <v>1076042.998577425</v>
       </c>
     </row>
     <row r="269">
@@ -12426,19 +12472,19 @@
         <v>1017.228576695272</v>
       </c>
       <c r="E269" s="33" t="n">
-        <v>40.07602197251683</v>
+        <v>40.27300828852613</v>
       </c>
       <c r="F269" s="22" t="n">
-        <v>930207.7255633922</v>
+        <v>1057509.698089116</v>
       </c>
       <c r="G269" s="22" t="n">
-        <v>1858.92830848</v>
+        <v>2113.328733191679</v>
       </c>
       <c r="H269" s="24" t="n">
-        <v>133.0828737186033</v>
+        <v>128.0828737186033</v>
       </c>
       <c r="I269" s="22" t="n">
-        <v>969604.9887652519</v>
+        <v>1096906.961290976</v>
       </c>
     </row>
     <row r="270">
@@ -12457,19 +12503,19 @@
         <v>1019.563890979194</v>
       </c>
       <c r="E270" s="34" t="n">
-        <v>7.962371261173675</v>
+        <v>8.001419188094305</v>
       </c>
       <c r="F270" s="25" t="n">
-        <v>203852.4787998703</v>
+        <v>234924.8969897964</v>
       </c>
       <c r="G270" s="25" t="n">
-        <v>407.3790543562556</v>
+        <v>469.4742146079064</v>
       </c>
       <c r="H270" s="27" t="n">
-        <v>129.059477265374</v>
+        <v>124.059477265374</v>
       </c>
       <c r="I270" s="25" t="n">
-        <v>211662.0641839962</v>
+        <v>242734.4823739223</v>
       </c>
     </row>
     <row r="271">
@@ -12488,19 +12534,19 @@
         <v>1024.996584701115</v>
       </c>
       <c r="E271" s="33" t="n">
-        <v>24.87623682952647</v>
+        <v>24.99758473058694</v>
       </c>
       <c r="F271" s="22" t="n">
-        <v>838057.6491100461</v>
+        <v>1012736.593040395</v>
       </c>
       <c r="G271" s="22" t="n">
-        <v>1674.775477837822</v>
+        <v>2023.854102798551</v>
       </c>
       <c r="H271" s="24" t="n">
-        <v>119.6832047961655</v>
+        <v>114.6832047961655</v>
       </c>
       <c r="I271" s="22" t="n">
-        <v>862327.2293221405</v>
+        <v>1037006.173252489</v>
       </c>
     </row>
     <row r="272">
@@ -12515,17 +12561,17 @@
       <c r="C272" s="16" t="inlineStr"/>
       <c r="D272" s="16" t="inlineStr"/>
       <c r="E272" s="35" t="n">
-        <v>208.7649323080833</v>
+        <v>209.7940098951366</v>
       </c>
       <c r="F272" s="28" t="n">
-        <v>4518234.143396341</v>
+        <v>5128446.614678579</v>
       </c>
       <c r="G272" s="28" t="n">
-        <v>9029.24489087998</v>
+        <v>10248.69427393801</v>
       </c>
       <c r="H272" s="16" t="inlineStr"/>
       <c r="I272" s="28" t="n">
-        <v>4724049.660807002</v>
+        <v>5334262.132089241</v>
       </c>
     </row>
     <row r="273">
@@ -12979,7 +13025,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>3 sets  |  total steam = 288,279 lb/hr  |  total condenser injection water = 6,084,253 lb/hr (12,159 GPM)</t>
+          <t>3 sets  |  total steam = 288,279 lb/hr  |  total condenser injection water = 6,922,616 lb/hr (13,834 GPM)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -13812,7 +13858,7 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>143472412.6263661</v>
+        <v>144177516.4375404</v>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
@@ -13842,7 +13888,7 @@
         </is>
       </c>
       <c r="B83" s="30" t="n">
-        <v>132.8134936467732</v>
+        <v>127.8134936467732</v>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
@@ -13857,7 +13903,7 @@
         </is>
       </c>
       <c r="B84" s="7" t="n">
-        <v>3351102.664269011</v>
+        <v>3812858.917093043</v>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
@@ -13872,7 +13918,7 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>6696.847850257815</v>
+        <v>7619.622136476904</v>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
@@ -13887,7 +13933,7 @@
         </is>
       </c>
       <c r="B86" s="7" t="n">
-        <v>3492123.426503871</v>
+        <v>3953879.679327903</v>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
@@ -14783,7 +14829,7 @@
         </is>
       </c>
       <c r="B171" s="7" t="n">
-        <v>68128571.9476818</v>
+        <v>68463393.9169427</v>
       </c>
       <c r="C171" s="8" t="inlineStr">
         <is>
@@ -14813,7 +14859,7 @@
         </is>
       </c>
       <c r="B173" s="30" t="n">
-        <v>132.8134936467732</v>
+        <v>127.8134936467732</v>
       </c>
       <c r="C173" s="8" t="inlineStr">
         <is>
@@ -14828,7 +14874,7 @@
         </is>
       </c>
       <c r="B174" s="7" t="n">
-        <v>1591287.375652338</v>
+        <v>1810554.574948273</v>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
@@ -14843,7 +14889,7 @@
         </is>
       </c>
       <c r="B175" s="7" t="n">
-        <v>3180.030726723297</v>
+        <v>3618.214578233958</v>
       </c>
       <c r="C175" s="8" t="inlineStr">
         <is>
@@ -14858,7 +14904,7 @@
         </is>
       </c>
       <c r="B176" s="7" t="n">
-        <v>1658251.769504519</v>
+        <v>1877518.968800454</v>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
@@ -15656,7 +15702,7 @@
         </is>
       </c>
       <c r="B266" s="7" t="n">
-        <v>48887142.44488114</v>
+        <v>49127401.25021033</v>
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
@@ -15686,7 +15732,7 @@
         </is>
       </c>
       <c r="B268" s="30" t="n">
-        <v>132.8134936467732</v>
+        <v>127.8134936467732</v>
       </c>
       <c r="C268" s="8" t="inlineStr">
         <is>
@@ -15701,7 +15747,7 @@
         </is>
       </c>
       <c r="B269" s="7" t="n">
-        <v>1141862.956763533</v>
+        <v>1299202.917062456</v>
       </c>
       <c r="C269" s="8" t="inlineStr">
         <is>
@@ -15716,7 +15762,7 @@
         </is>
       </c>
       <c r="B270" s="7" t="n">
-        <v>2281.900393212496</v>
+        <v>2596.328771108025</v>
       </c>
       <c r="C270" s="8" t="inlineStr">
         <is>
@@ -15731,7 +15777,7 @@
         </is>
       </c>
       <c r="B271" s="7" t="n">
-        <v>1189914.71782937</v>
+        <v>1347254.678128293</v>
       </c>
       <c r="C271" s="8" t="inlineStr">
         <is>
